--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5184,10 +5184,10 @@
         <v>1.6</v>
       </c>
       <c r="M40" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="N41" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N51" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="M59" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="N59" t="n">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.78</v>
+        <v>1.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>5.7</v>
+        <v>1.98</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="M62" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="N62" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N63" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,55 +8037,55 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB64" t="n">
         <v>1.94</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N106" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,14 +13630,14 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N111" t="n">
         <v>2.3</v>
       </c>
-      <c r="M111" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3447,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="M43" t="n">
-        <v>4.05</v>
+        <v>7.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6493,7 +6493,7 @@
         <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="N51" t="n">
         <v>3.25</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="M59" t="n">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N61" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="M62" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="N62" t="n">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M63" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,55 +8156,55 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB65" t="n">
         <v>1.94</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11729,10 +11729,10 @@
         <v>4.3</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,16 +12842,16 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,14 +13749,14 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N112" t="n">
         <v>2.3</v>
       </c>
-      <c r="M112" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3447,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4161,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="M43" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="N43" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="N45" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M59" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N60" t="n">
-        <v>5.7</v>
+        <v>1.41</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M62" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.56</v>
+        <v>2.5</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,55 +8037,55 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB64" t="n">
         <v>1.94</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M70" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,14 +13630,14 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N111" t="n">
         <v>2.3</v>
       </c>
-      <c r="M111" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3566,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4161,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>14</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="M43" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.64</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="N57" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M58" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N58" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N59" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M60" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.78</v>
+        <v>2.5</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>2.9</v>
       </c>
       <c r="N61" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N62" t="n">
-        <v>5.7</v>
+        <v>1.41</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N63" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N70" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,16 +12842,16 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,14 +13749,14 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N112" t="n">
         <v>2.3</v>
       </c>
-      <c r="M112" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2019,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3566,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC33" t="n">
         <v>2.15</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M40" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M57" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.78</v>
+        <v>1.6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.5</v>
+        <v>3.78</v>
       </c>
       <c r="M61" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N61" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M63" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N63" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB63" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M70" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M74" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="N105" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2019,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="M43" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>17</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="N45" t="n">
-        <v>4.33</v>
+        <v>14</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M56" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N56" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.64</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="N57" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.56</v>
+        <v>2.5</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>6.6</v>
+        <v>3.78</v>
       </c>
       <c r="M62" t="n">
-        <v>3.88</v>
+        <v>3.47</v>
       </c>
       <c r="N62" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="N63" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="M71" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,14 +13630,14 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N111" t="n">
         <v>2.3</v>
       </c>
-      <c r="M111" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="M45" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="N45" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N59" t="n">
-        <v>5.7</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.5</v>
+        <v>3.78</v>
       </c>
       <c r="M60" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.78</v>
+        <v>2.5</v>
       </c>
       <c r="M62" t="n">
-        <v>3.47</v>
+        <v>2.9</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N63" t="n">
-        <v>1.41</v>
+        <v>5.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,16 +11890,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,14 +13749,14 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N112" t="n">
         <v>2.3</v>
       </c>
-      <c r="M112" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="M40" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="N40" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>14</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="M59" t="n">
-        <v>3.88</v>
+        <v>2.9</v>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M60" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N61" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>3.78</v>
       </c>
       <c r="M62" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N62" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,16 +11890,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N106" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="M59" t="n">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N60" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M61" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.78</v>
+        <v>1.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M63" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N63" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB63" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M66" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N66" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="N68" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M74" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,14 +13630,14 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N111" t="n">
         <v>2.3</v>
       </c>
-      <c r="M111" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>2.89</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,16 +4506,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M40" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="M43" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M59" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N61" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N62" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N63" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M66" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4042,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,10 +4982,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.93</v>
       </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="M43" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="N43" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.56</v>
+        <v>2.45</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M60" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6.6</v>
+        <v>3.78</v>
       </c>
       <c r="M61" t="n">
-        <v>3.88</v>
+        <v>3.47</v>
       </c>
       <c r="N61" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M62" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N63" t="n">
-        <v>5.7</v>
+        <v>1.41</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB63" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.05</v>
+        <v>1.11</v>
       </c>
       <c r="M97" t="n">
-        <v>3.04</v>
+        <v>9.5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M105" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N105" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="N106" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI118"/>
+  <dimension ref="A1:AI121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,10 +4982,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4.33</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.45</v>
+        <v>3.78</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.56</v>
+        <v>1.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>2.01</v>
+        <v>5.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.78</v>
+        <v>2.45</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N62" t="n">
-        <v>5.7</v>
+        <v>1.41</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M63" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="N69" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.05</v>
+        <v>1.11</v>
       </c>
       <c r="M103" t="n">
-        <v>3.04</v>
+        <v>9.5</v>
       </c>
       <c r="N103" t="n">
-        <v>2.16</v>
+        <v>15</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M111" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,14 +13749,14 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N112" t="n">
         <v>2.3</v>
       </c>
-      <c r="M112" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N112" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14437,102 +14437,459 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Chapelton</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" s="3" t="n">
+        <v>46033.70833333334</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" s="3" t="n">
+        <v>46033.70833333334</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" s="3" t="n">
+        <v>46033.70833333334</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="inlineStr">
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI118" s="3" t="n">
-        <v>46033.8125</v>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" s="3" t="n">
+        <v>46033.70833333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,10 +4982,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="N42" t="n">
-        <v>4.33</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>6.2</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,16 +7011,16 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M62" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="N72" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N106" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,10 +4982,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5351,10 +5351,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="N44" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,16 +7011,16 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M57" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.78</v>
+        <v>1.6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.45</v>
+        <v>3.78</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N61" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M80" t="n">
         <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,16 +12366,16 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="M106" t="n">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="N106" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC113" t="n">
         <v>1.92</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G120" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>6.2</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M51" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.45</v>
+        <v>6.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>3.88</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>1.41</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N62" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.6</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M81" t="n">
         <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,16 +12366,16 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N106" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3566,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>6.6</v>
+        <v>2.45</v>
       </c>
       <c r="M60" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N61" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.78</v>
+        <v>6.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.47</v>
+        <v>3.88</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.45</v>
+        <v>3.56</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M69" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N74" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,16 +12723,16 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G120" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3566,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="N42" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="M45" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="N45" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB45" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.6</v>
+        <v>3.78</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N59" t="n">
-        <v>5.7</v>
+        <v>1.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>1.41</v>
+        <v>5.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="N67" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="M70" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="M101" t="n">
-        <v>9.5</v>
+        <v>3.04</v>
       </c>
       <c r="N101" t="n">
-        <v>15</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AB101" t="n">
-        <v>3.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="N108" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
         <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.89</v>
+        <v>2.33</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>2.35</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>6.2</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="N43" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.64</v>
+        <v>2.25</v>
       </c>
       <c r="M57" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M59" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N61" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.6</v>
+        <v>3.78</v>
       </c>
       <c r="M63" t="n">
-        <v>3.88</v>
+        <v>3.47</v>
       </c>
       <c r="N63" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="N70" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="M71" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M79" t="n">
         <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M81" t="n">
         <v>3</v>
       </c>
-      <c r="M81" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N81" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="M101" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N101" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.15</v>
+        <v>2.43</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>1.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>7.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3447,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>1.77</v>
       </c>
       <c r="M26" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="M34" t="n">
         <v>2.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>2.35</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="M40" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>17</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.38</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,55 +7085,55 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB56" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.82</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="M57" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.56</v>
+        <v>2.45</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.45</v>
+        <v>3.78</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N62" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M63" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="M69" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N71" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M79" t="n">
         <v>3</v>
       </c>
-      <c r="M79" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N79" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N88" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="M89" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N89" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="M92" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="N92" t="n">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="M97" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N97" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>2.85</v>
+        <v>5.2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="M101" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N101" t="n">
-        <v>5.2</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="M102" t="n">
-        <v>9.5</v>
+        <v>4.1</v>
       </c>
       <c r="N102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,16 +12604,16 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB102" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>2.18</v>
+        <v>2.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="M105" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N105" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="M106" t="n">
         <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M108" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N108" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,14 +13630,14 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N111" t="n">
         <v>2.3</v>
       </c>
-      <c r="M111" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O111" t="n">
         <v>0</v>
       </c>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M112" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.44</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>7.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N20" t="n">
         <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>2.43</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>7.6</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>3.3</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3447,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
         <v>3.2</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>1.63</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N36" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="M37" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M40" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="N42" t="n">
-        <v>4.33</v>
+        <v>17</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M44" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N53" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="N55" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M56" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N56" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>3.86</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.45</v>
+        <v>3.78</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.6</v>
+        <v>3.56</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>5.7</v>
+        <v>2.01</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6.6</v>
+        <v>2.45</v>
       </c>
       <c r="M61" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>1.41</v>
+        <v>2.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.78</v>
+        <v>1.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="M66" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="M71" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N71" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.7</v>
+        <v>3.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>4.8</v>
+        <v>1.93</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M74" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N74" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M78" t="n">
         <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M84" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="M85" t="n">
         <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M86" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N86" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="M87" t="n">
         <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="M88" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="N88" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="M89" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N89" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="M90" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N90" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="M91" t="n">
         <v>2.85</v>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.75</v>
+        <v>2.31</v>
       </c>
       <c r="M94" t="n">
         <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="M96" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.11</v>
+        <v>2.25</v>
       </c>
       <c r="M98" t="n">
-        <v>9.5</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>15</v>
+        <v>2.85</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB98" t="n">
-        <v>3.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>9.5</v>
       </c>
       <c r="N99" t="n">
-        <v>2.18</v>
+        <v>15</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="M102" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>10</v>
+        <v>2.95</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N103" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="M105" t="n">
         <v>3.1</v>
       </c>
       <c r="N105" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="M106" t="n">
         <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="M107" t="n">
-        <v>5.1</v>
+        <v>3.13</v>
       </c>
       <c r="N107" t="n">
-        <v>1.3</v>
+        <v>2.18</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>3.13</v>
+        <v>5.1</v>
       </c>
       <c r="N108" t="n">
-        <v>2.18</v>
+        <v>1.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46033.3125</v>
+        <v>46033.25</v>
       </c>
     </row>
     <row r="7">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46033.33333333334</v>
+        <v>46033.3125</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>2.09</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,55 +1849,55 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.95</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.23</v>
+        <v>3.64</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.43</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>7.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.9</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.63</v>
+        <v>2.43</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="N29" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>46033.34375</v>
+        <v>46033.33333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46033.35416666666</v>
+        <v>46033.34375</v>
       </c>
     </row>
     <row r="35">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="M36" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="M39" t="n">
         <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.33</v>
+        <v>2.89</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46033.375</v>
+        <v>46033.35416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>7.8</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="M43" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB43" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46033.38541666666</v>
+        <v>46033.375</v>
       </c>
     </row>
     <row r="47">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>8.5</v>
+        <v>2.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N52" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="N53" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="N55" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.64</v>
+        <v>2.55</v>
       </c>
       <c r="M56" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="M58" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N58" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.78</v>
+        <v>2.45</v>
       </c>
       <c r="M59" t="n">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="N60" t="n">
-        <v>2.01</v>
+        <v>1.41</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N61" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.6</v>
+        <v>3.78</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N62" t="n">
-        <v>5.7</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>6.6</v>
+        <v>3.56</v>
       </c>
       <c r="M63" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="N63" t="n">
-        <v>1.41</v>
+        <v>2.01</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="N69" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="M71" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="N72" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M78" t="n">
         <v>3</v>
       </c>
-      <c r="M78" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N78" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M80" t="n">
         <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N84" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N85" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="M86" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="M87" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N87" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="M88" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="M89" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N89" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="M90" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N90" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11253,10 +11253,10 @@
         <v>2.31</v>
       </c>
       <c r="M91" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="M93" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N93" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="N96" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.9</v>
+        <v>1.11</v>
       </c>
       <c r="M97" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.25</v>
+        <v>15</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="N98" t="n">
-        <v>2.85</v>
+        <v>10</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="M99" t="n">
-        <v>9.5</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>15</v>
+        <v>2.18</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="M101" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N102" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="M103" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="M104" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N104" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="M105" t="n">
         <v>3.1</v>
       </c>
       <c r="N105" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="M106" t="n">
         <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M109" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N110" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -668,46 +668,46 @@
         <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC2" t="n">
         <v>2.2</v>
@@ -716,16 +716,16 @@
         <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46033.125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="M11" t="n">
         <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>7.6</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.95</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>7.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.64</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="M32" t="n">
         <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,16 +5101,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="M40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.25</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.7</v>
+        <v>8.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="M52" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N52" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.64</v>
+        <v>2.55</v>
       </c>
       <c r="M54" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,55 +7204,55 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB57" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.82</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.38</v>
+        <v>3.64</v>
       </c>
       <c r="M58" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="N58" t="n">
-        <v>8.5</v>
+        <v>1.87</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>6.6</v>
+        <v>3.78</v>
       </c>
       <c r="M60" t="n">
-        <v>3.88</v>
+        <v>3.47</v>
       </c>
       <c r="N60" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="N61" t="n">
-        <v>5.7</v>
+        <v>1.41</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.78</v>
+        <v>3.56</v>
       </c>
       <c r="M62" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.56</v>
+        <v>1.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N63" t="n">
-        <v>2.01</v>
+        <v>5.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="M69" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="N69" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="M70" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M78" t="n">
         <v>3.2</v>
       </c>
-      <c r="M78" t="n">
-        <v>3</v>
-      </c>
       <c r="N78" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
         <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="M84" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N84" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="M85" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N85" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="M86" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N86" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="M87" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N87" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N88" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="M89" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N89" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="M90" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N90" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N91" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M92" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="M93" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="N93" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.11</v>
+        <v>2.25</v>
       </c>
       <c r="M97" t="n">
-        <v>9.5</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>15</v>
+        <v>2.85</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,16 +12009,16 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AB97" t="n">
-        <v>3.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="M100" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>5.2</v>
+        <v>2.95</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="N101" t="n">
-        <v>2.95</v>
+        <v>15</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,16 +12485,16 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="M102" t="n">
         <v>3.2</v>
       </c>
       <c r="N102" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M103" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N103" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="N105" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N106" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="M107" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N107" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>11</v>
+        <v>3.75</v>
       </c>
       <c r="M108" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="N108" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N109" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="M110" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N114" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,14 +2325,14 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N16" t="n">
         <v>4.4</v>
       </c>
-      <c r="N16" t="n">
-        <v>7.6</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>9.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>7.2</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>4.38</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
         <v>3.2</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
         <v>3.2</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.03</v>
+        <v>3.25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
         <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46033.35416666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N51" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,55 +6609,55 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB52" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="M55" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N55" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M57" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="M60" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46033.45833333334</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="M77" t="n">
         <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M79" t="n">
         <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="M107" t="n">
         <v>3.1</v>
       </c>
       <c r="N107" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="M108" t="n">
         <v>3.1</v>
       </c>
       <c r="N108" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.15</v>
+        <v>2.11</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>3.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M51" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N57" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="M61" t="n">
-        <v>3.88</v>
+        <v>4.17</v>
       </c>
       <c r="N61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O61" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U61" t="n">
         <v>1.41</v>
       </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46033.45833333334</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="M107" t="n">
         <v>3.1</v>
       </c>
       <c r="N107" t="n">
-        <v>1.93</v>
+        <v>2.41</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="M108" t="n">
         <v>3.1</v>
       </c>
       <c r="N108" t="n">
-        <v>2.41</v>
+        <v>1.93</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G117" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -677,10 +677,10 @@
         <v>4.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="T2" t="n">
         <v>2.14</v>
@@ -698,10 +698,10 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.53</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
         <v>1.5</v>
@@ -719,13 +719,13 @@
         <v>1.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46033.125</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.15</v>
+        <v>2.01</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>2.09</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M18" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46033.33333333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>2.58</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="N20" t="n">
-        <v>9.65</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>2.43</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.64</v>
+        <v>2.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>8.050000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.38</v>
+        <v>2.23</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>4.38</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.01</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>9.65</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.45</v>
       </c>
-      <c r="N35" t="n">
+      <c r="U35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE35" t="n">
         <v>2.03</v>
       </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46033.35416666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>3.25</v>
+        <v>2.03</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="M38" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46033.35416666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46033.35416666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N40" t="n">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="O40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46033.35416666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46033.375</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46033.375</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="N43" t="n">
-        <v>5.2</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46033.375</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5785,40 +5785,40 @@
         <v>17</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA45" t="n">
         <v>1.36</v>
@@ -5833,16 +5833,16 @@
         <v>1.84</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46033.375</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.17</v>
+        <v>1.81</v>
       </c>
       <c r="M46" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,16 +5940,16 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="M50" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="N50" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46033.4375</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.85</v>
+        <v>3.64</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="N51" t="n">
-        <v>3.7</v>
+        <v>1.87</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,16 +6535,16 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N53" t="n">
-        <v>2.45</v>
+        <v>8.5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46033.4375</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>3.82</v>
       </c>
       <c r="N54" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46033.4375</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46033.4375</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7207,70 +7207,70 @@
         <v>2.1</v>
       </c>
       <c r="M57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N57" t="n">
         <v>2.9</v>
       </c>
-      <c r="N57" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46033.4375</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>3.86</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P58" t="n">
         <v>1.87</v>
       </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>4.25</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46033.4375</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.45</v>
+        <v>3.56</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
-        <v>2.75</v>
+        <v>2.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M60" t="n">
         <v>3.8</v>
       </c>
-      <c r="M60" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N60" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB60" t="n">
         <v>2</v>
       </c>
-      <c r="O60" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T60" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V60" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46033.45833333334</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46033.45833333334</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M63" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>5.7</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB63" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46033.45833333334</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>3.57</v>
+        <v>2.04</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA64" t="n">
         <v>1.79</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46033.47916666666</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N65" t="n">
-        <v>2.04</v>
+        <v>3.57</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8204,7 +8204,7 @@
         <v>1.79</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="M69" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N71" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="M72" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="M74" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N75" t="n">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46033.52083333334</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="M79" t="n">
         <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M80" t="n">
         <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="M84" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N84" t="n">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="M85" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N85" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="M87" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N87" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="M88" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N88" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="M90" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N90" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="M91" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N91" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="M92" t="n">
         <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,73 +11964,73 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M97" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>2.85</v>
+        <v>5.2</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI97" s="3" t="n">
         <v>46033.5625</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="M98" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="N98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,16 +12128,16 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,73 +12202,73 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI99" s="3" t="n">
         <v>46033.5625</v>
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,73 +12321,73 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="M100" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N100" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AI100" s="3" t="n">
         <v>46033.5625</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,73 +12440,73 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="M101" t="n">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>15</v>
+        <v>2.95</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB101" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI101" s="3" t="n">
         <v>46033.5625</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,73 +12678,73 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N103" t="n">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI103" s="3" t="n">
         <v>46033.5625</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>3.75</v>
       </c>
       <c r="M105" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="N105" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="M106" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.65</v>
+        <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="N107" t="n">
-        <v>2.41</v>
+        <v>1.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,73 +13273,73 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="M108" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N108" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O108" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P108" t="n">
         <v>1.93</v>
       </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI108" s="3" t="n">
         <v>46033.58333333334</v>
@@ -13639,40 +13639,40 @@
         <v>2.3</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA111" t="n">
         <v>2.12</v>
@@ -13681,22 +13681,22 @@
         <v>1.64</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI111" s="3" t="n">
         <v>46033.625</v>
@@ -13987,49 +13987,49 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M114" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="N114" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA114" t="n">
         <v>1.9</v>
@@ -14038,22 +14038,22 @@
         <v>1.8</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG114" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI114" s="3" t="n">
         <v>46033.6875</v>
@@ -14106,73 +14106,73 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="M115" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="N115" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI115" s="3" t="n">
         <v>46033.69791666666</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-01-11.xlsx
+++ b/jogos_2026-01-11.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.33</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46033.3125</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46033.33333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46033.33333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46033.33333333334</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.95</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>7.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46033.33333333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V20" t="n">
+        <v>10</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.58</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46033.33333333334</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,55 +2920,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.43</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
       <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.75</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>8.050000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.23</v>
+        <v>3.64</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.75</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46033.33333333334</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.34</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.75</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>4.38</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46033.33333333334</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>9.65</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="O35" t="n">
         <v>3.48</v>
@@ -4625,16 +4625,16 @@
         <v>1.08</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AC35" t="n">
         <v>4.6</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.96</v>
+        <v>2.15</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.03</v>
+        <v>2.85</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46033.35416666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46033.35416666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O41" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.51</v>
+        <v>12</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="S41" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="V41" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="W41" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.57</v>
+        <v>5.1</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46033.375</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N42" t="n">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="P42" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="R42" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="T42" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V42" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="W42" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.97</v>
+        <v>2.76</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46033.375</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.17</v>
+        <v>1.81</v>
       </c>
       <c r="M43" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46033.375</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N44" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46033.375</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46033.375</v>
@@ -6023,40 +6023,40 @@
         <v>3.1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA47" t="n">
         <v>2.35</v>
@@ -6065,22 +6065,22 @@
         <v>1.53</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46033.41666666666</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,61 +6371,61 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V50" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA50" t="n">
         <v>2.25</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P50" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V50" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB50" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE50" t="n">
         <v>1.95</v>
@@ -6437,7 +6437,7 @@
         <v>1.3</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46033.4375</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46033.4375</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46033.4375</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="M54" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="M55" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T55" t="n">
         <v>3.2</v>
       </c>
-      <c r="N55" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.92</v>
-      </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V55" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W55" t="n">
         <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46033.4375</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,28 +7085,28 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O56" t="n">
-        <v>2.53</v>
+        <v>3.15</v>
       </c>
       <c r="P56" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.72</v>
+        <v>3.32</v>
       </c>
       <c r="R56" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S56" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="T56" t="n">
         <v>2.92</v>
@@ -7115,25 +7115,25 @@
         <v>1.32</v>
       </c>
       <c r="V56" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="W56" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X56" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
         <v>3.5</v>
@@ -7142,16 +7142,16 @@
         <v>1.22</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46033.4375</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,73 +7204,73 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N57" t="n">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="O57" t="n">
-        <v>2.53</v>
+        <v>1.87</v>
       </c>
       <c r="P57" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V57" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V57" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB57" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.72</v>
+        <v>3</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46033.4375</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-       